--- a/data/trans_dic/IP12B$vomitos-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,18</t>
+          <t>0,0; 19,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,35</t>
+          <t>0,0; 42,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,03</t>
+          <t>0,0; 33,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,85</t>
+          <t>0,0; 24,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,6</t>
+          <t>0,0; 16,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,51</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,86</t>
+          <t>0,0; 17,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,32</t>
+          <t>0,0; 15,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 10,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,7</t>
+          <t>0,0; 8,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,0; 9,5</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,62</t>
+          <t>0,0; 23,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,96</t>
+          <t>0,0; 24,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,34</t>
+          <t>0,0; 14,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,6</t>
+          <t>0,0; 13,35</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,73</t>
+          <t>0,0; 40,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,41</t>
+          <t>0,0; 43,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,99</t>
+          <t>0,0; 26,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,18</t>
+          <t>0,0; 25,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,23</t>
+          <t>0,0; 18,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,36</t>
+          <t>1,38; 12,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 7,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,25</t>
+          <t>1,36; 11,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,53</t>
+          <t>1,01; 9,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 7,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,75</t>
+          <t>2,02; 9,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,08</t>
+          <t>1,05; 6,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,71</t>
+          <t>0,54; 5,31</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3534</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3956</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4378</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4588</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5081</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3477</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3533</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3608</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3923</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3939</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3894</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2483</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3503</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3005</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3482</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3256</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3387</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3991</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3952</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4438</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4291</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>607; 5510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4823</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3944</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>637; 5211</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>642; 6073</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3509</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1827; 8285</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1313; 7923</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>558; 5471</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$vomitos-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,67</t>
+          <t>0,0; 15,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,43</t>
+          <t>0,0; 42,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,08</t>
+          <t>0,0; 31,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,86</t>
+          <t>0,0; 25,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>0,0; 17,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>0,0; 22,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,45</t>
+          <t>0,0; 24,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,88</t>
+          <t>0,0; 15,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 10,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,68</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,5</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,11</t>
+          <t>0,0; 21,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,94</t>
+          <t>0,0; 21,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,51</t>
+          <t>0,0; 13,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,35</t>
+          <t>0,0; 16,42</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,99</t>
+          <t>0,0; 40,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,46</t>
+          <t>0,0; 40,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,63</t>
+          <t>0,0; 26,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,11</t>
+          <t>0,0; 27,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,44</t>
+          <t>0,0; 16,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,56</t>
+          <t>1,45; 13,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,15</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,16</t>
+          <t>1,37; 11,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,56</t>
+          <t>1,01; 10,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,15</t>
+          <t>2,06; 9,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,35</t>
+          <t>1,03; 6,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,31</t>
+          <t>0,54; 4,67</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por vómitos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3534</t>
+          <t>0; 2785</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3956</t>
+          <t>0; 3949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4378</t>
+          <t>0; 4126</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4588</t>
+          <t>0; 4658</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5081</t>
+          <t>0; 5402</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3477</t>
+          <t>0; 3589</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3533</t>
+          <t>0; 4952</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3608</t>
+          <t>0; 3583</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 3771</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3939</t>
+          <t>0; 4387</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3894</t>
+          <t>0; 3430</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2483</t>
+          <t>0; 2324</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3503</t>
+          <t>0; 3026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3005</t>
+          <t>0; 2843</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3482</t>
+          <t>0; 4282</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3256</t>
+          <t>0; 3247</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3387</t>
+          <t>0; 3144</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3991</t>
+          <t>0; 3964</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3952</t>
+          <t>0; 4374</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 3996</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>607; 5510</t>
+          <t>634; 5999</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 5561</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 3824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>637; 5211</t>
+          <t>639; 5435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>642; 6073</t>
+          <t>640; 6486</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3509</t>
+          <t>0; 3728</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1827; 8285</t>
+          <t>1864; 8578</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1313; 7923</t>
+          <t>1286; 8131</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>558; 5471</t>
+          <t>559; 4812</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$vomitos-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$vomitos-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,5</t>
+          <t>0,0; 34,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,17</t>
+          <t>0,0; 18,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,24</t>
+          <t>0,0; 25,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,31</t>
+          <t>0,0; 16,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,89%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,97%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 25,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 16,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,57</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 8,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,9%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,73</t>
+          <t>0,0; 13,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,42</t>
+          <t>0,0; 13,6</t>
         </is>
       </c>
     </row>
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>8,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,87</t>
+          <t>0,0; 41,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 26,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,35</t>
+          <t>0,0; 39,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,79</t>
+          <t>0,0; 24,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,61</t>
+          <t>0,0; 16,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,27%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,67</t>
+          <t>1,35; 11,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,07</t>
+          <t>1,01; 9,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 7,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,64</t>
+          <t>1,23; 12,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,21</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,47</t>
+          <t>2,1; 9,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,51</t>
+          <t>1,03; 7,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,67</t>
+          <t>0,54; 4,71</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1364,27 +1364,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3949</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2785</t>
+          <t>0; 4504</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3949</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>0; 3267</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4658</t>
+          <t>0; 4770</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5402</t>
+          <t>0; 5178</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1133</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1128</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3589</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4952</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3583</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3210</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3708</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3771</t>
+          <t>0; 3682</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4387</t>
+          <t>0; 3948</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3430</t>
+          <t>0; 3416</t>
         </is>
       </c>
     </row>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,24 +1690,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2324</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3026</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2843</t>
+          <t>0; 2763</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4282</t>
+          <t>0; 3545</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3247</t>
+          <t>0; 3227</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4045</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3144</t>
+          <t>0; 3157</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3964</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4374</t>
+          <t>0; 3805</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3996</t>
+          <t>0; 3904</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2313</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1414</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1128</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>634; 5999</t>
+          <t>631; 5254</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5561</t>
+          <t>644; 6058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3824</t>
+          <t>0; 3707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>639; 5435</t>
+          <t>538; 5422</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>640; 6486</t>
+          <t>0; 4968</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3728</t>
+          <t>0; 3582</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1864; 8578</t>
+          <t>1904; 8831</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1286; 8131</t>
+          <t>1284; 8837</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>559; 4812</t>
+          <t>557; 4848</t>
         </is>
       </c>
     </row>
